--- a/StructureDefinition-SEEHDSTask.xlsx
+++ b/StructureDefinition-SEEHDSTask.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T07:04:04+00:00</t>
+    <t>2026-10-06T07:20:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSTask.xlsx
+++ b/StructureDefinition-SEEHDSTask.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T07:20:43+00:00</t>
+    <t>2026-10-07T11:41:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSTask.xlsx
+++ b/StructureDefinition-SEEHDSTask.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T11:41:58+00:00</t>
+    <t>2026-10-07T11:49:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSTask.xlsx
+++ b/StructureDefinition-SEEHDSTask.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T11:49:57+00:00</t>
+    <t>2026-10-09T07:52:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -420,7 +420,7 @@
 </t>
   </si>
   <si>
-    <t>Källsystem HSA-id (requestHeader.sourceSystemHSAId) – https://tjanstekatalogen.inera.se/Endpoint/{hsaId} (GENERAL-005)</t>
+    <t>Källsystem (requestActivity.header.sourceSystemId.extension) – https://tjanstekatalogen.inera.se/Endpoint/{hsaId} (GENERAL-005)</t>
   </si>
   <si>
     <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
@@ -631,7 +631,7 @@
 </t>
   </si>
   <si>
-    <t>Task Instance Identifier</t>
+    <t>Remisstatusens id (header.record.id)</t>
   </si>
   <si>
     <t>The business identifier for this task.</t>
@@ -745,7 +745,7 @@
     <t>Task.status</t>
   </si>
   <si>
-    <t>Aktivitetsstatus (requestStatus – kv_requestStatus)</t>
+    <t>Status härledd från body.statusCode (Kv status vårdbegäran)</t>
   </si>
   <si>
     <t>The current status of the task.</t>
@@ -794,7 +794,7 @@
     <t>Task.businessStatus</t>
   </si>
   <si>
-    <t>E.g. "Specimen collected", "IV prepped"</t>
+    <t>Remisstatus enligt Kv status vårdbegäran (body.statusCode)</t>
   </si>
   <si>
     <t>Contains business-specific nuances of the business state.</t>
@@ -870,7 +870,7 @@
     <t>Task.code</t>
   </si>
   <si>
-    <t>Aktivitetstyp (activityType)</t>
+    <t>Task Type</t>
   </si>
   <si>
     <t>A name or code (or both) briefly describing what the task involves.</t>
@@ -897,7 +897,7 @@
     <t>Task.description</t>
   </si>
   <si>
-    <t>Aktivitetsbeskrivning (activityComment)</t>
+    <t>Human-readable explanation of task</t>
   </si>
   <si>
     <t>A free-text description of what is to be performed.</t>
@@ -913,7 +913,7 @@
 </t>
   </si>
   <si>
-    <t>Koppling till remiss (requestId)</t>
+    <t>Koppling till remiss (body.request.id)</t>
   </si>
   <si>
     <t>The request being actioned or the resource being manipulated by this task.</t>
@@ -939,7 +939,7 @@
 </t>
   </si>
   <si>
-    <t>Patient (requestHeader.patientId)</t>
+    <t>Patient – den efterfrågade patienten (begärans patientId); svaret saknar patientidentitet</t>
   </si>
   <si>
     <t>The entity who benefits from the performance of the service specified in the task (e.g., the patient).</t>
@@ -1015,7 +1015,7 @@
 </t>
   </si>
   <si>
-    <t>Registreringsdatum (requestHeader.documentTime)</t>
+    <t>Skapad i källsystemet (header.record.timestamp)</t>
   </si>
   <si>
     <t>The date and time this task was created.</t>
@@ -1044,7 +1044,7 @@
 </t>
   </si>
   <si>
-    <t>Senaste statusändring (activityTime)</t>
+    <t>Statusändring (body.eventTime)</t>
   </si>
   <si>
     <t>The date and time of last modification to this task.</t>
@@ -1063,7 +1063,7 @@
 </t>
   </si>
   <si>
-    <t>Who is asking for task to be done</t>
+    <t>Remittent (body.request.author)</t>
   </si>
   <si>
     <t>The creator of the task.</t>
@@ -1119,7 +1119,7 @@
 </t>
   </si>
   <si>
-    <t>Mottagande enhet (requestReceiver)</t>
+    <t>Mottagande enhet (body.request.receivingOrganization)</t>
   </si>
   <si>
     <t>Individual organization or Device currently responsible for task execution.</t>
@@ -3891,7 +3891,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
         <v>195</v>
       </c>
@@ -3910,7 +3910,7 @@
         <v>79</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>77</v>
@@ -4801,7 +4801,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
         <v>249</v>
       </c>
@@ -4820,7 +4820,7 @@
         <v>87</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>77</v>
@@ -5145,7 +5145,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
         <v>274</v>
       </c>
@@ -5164,7 +5164,7 @@
         <v>87</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>77</v>
@@ -5259,7 +5259,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
         <v>283</v>
       </c>
@@ -5278,7 +5278,7 @@
         <v>87</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>77</v>
@@ -6055,7 +6055,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
         <v>334</v>
       </c>
@@ -6074,7 +6074,7 @@
         <v>87</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>77</v>

--- a/StructureDefinition-SEEHDSTask.xlsx
+++ b/StructureDefinition-SEEHDSTask.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.3</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T07:52:45+00:00</t>
+    <t>2026-10-12T12:51:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSTask.xlsx
+++ b/StructureDefinition-SEEHDSTask.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T12:51:47+00:00</t>
+    <t>2026-10-12T13:38:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSTask.xlsx
+++ b/StructureDefinition-SEEHDSTask.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T13:38:08+00:00</t>
+    <t>2026-10-15T17:10:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSTask.xlsx
+++ b/StructureDefinition-SEEHDSTask.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T17:10:15+00:00</t>
+    <t>2026-10-15T18:03:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSTask.xlsx
+++ b/StructureDefinition-SEEHDSTask.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T18:03:33+00:00</t>
+    <t>2026-10-26T15:58:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
